--- a/docs/base/0.3.0/StructureDefinition-location-lt.xlsx
+++ b/docs/base/0.3.0/StructureDefinition-location-lt.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="332">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T18:57:53+02:00</t>
+    <t>2026-03-15T22:56:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.eu/fhir/base-r5/StructureDefinition/location-eu|2.0.0-ballot</t>
+    <t>http://hl7.eu/fhir/base-r5/StructureDefinition/location-eu-core|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -651,7 +651,7 @@
 </t>
   </si>
   <si>
-    <t>Location telecom</t>
+    <t>Official contact details for the location</t>
   </si>
   <si>
     <t>The contact details of communication devices available at the location. This can include addresses, phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
@@ -667,6 +667,154 @@
     <t>.telecom and .addr and other .role(relevant datatype properties mapped from role into extendedcontactdetail)</t>
   </si>
   <si>
+    <t>Location.contact.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Location.contact.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Location.contact.purpose</t>
+  </si>
+  <si>
+    <t>The type of contact</t>
+  </si>
+  <si>
+    <t>The purpose/type of contact.</t>
+  </si>
+  <si>
+    <t>If no purpose is defined, then these contact details may be used for any purpose.</t>
+  </si>
+  <si>
+    <t>The purpose for which an extended contact detail should be used.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/contactentity-type|2.0.0</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.purpose</t>
+  </si>
+  <si>
+    <t>Location.contact.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName
+</t>
+  </si>
+  <si>
+    <t>Name of an individual to contact</t>
+  </si>
+  <si>
+    <t>The name of an individual to contact, some types of contact detail are usually blank.</t>
+  </si>
+  <si>
+    <t>If there is no named individual, the telecom/address information is not generally monitored by a specific individual.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.name</t>
+  </si>
+  <si>
+    <t>Location.contact.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>Location telecom</t>
+  </si>
+  <si>
+    <t>The contact details application for the purpose defined.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.telecom</t>
+  </si>
+  <si>
+    <t>Location.contact.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Address for the contact</t>
+  </si>
+  <si>
+    <t>Address for the contact.</t>
+  </si>
+  <si>
+    <t>More than 1 address would be for different purposes, and thus should be entered as a different entry,.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.address</t>
+  </si>
+  <si>
+    <t>Location.contact.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|5.0.0)
+</t>
+  </si>
+  <si>
+    <t>This contact detail is handled/monitored by a specific organization</t>
+  </si>
+  <si>
+    <t>This contact detail is handled/monitored by a specific organization. If the name is provided in the contact, then it is referring to the named individual within this organization.</t>
+  </si>
+  <si>
+    <t>Some specific types of contact information can be an handled by an organization (eg legal council is via a specific firm).</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.organization</t>
+  </si>
+  <si>
+    <t>Location.contact.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Period that this contact was valid for usage</t>
+  </si>
+  <si>
+    <t>Period that this contact was valid for usage.</t>
+  </si>
+  <si>
+    <t>If the details have multiple periods, then enter in a new ExtendedContact with the new period.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.period</t>
+  </si>
+  <si>
     <t>Location.address</t>
   </si>
   <si>
@@ -741,26 +889,7 @@
     <t>Location.position.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Location.position.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Location.position.modifierExtension</t>
@@ -815,10 +944,6 @@
   </si>
   <si>
     <t>Location.managingOrganization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|5.0.0)
-</t>
   </si>
   <si>
     <t>Managing organization</t>
@@ -1235,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.59765625" customWidth="true" bestFit="true"/>
@@ -1266,7 +1391,7 @@
     <col min="26" max="26" width="62.05859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3421,20 +3546,16 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3482,7 +3603,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3491,38 +3612,38 @@
         <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3531,21 +3652,21 @@
         <v>75</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
@@ -3569,49 +3690,49 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>75</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>75</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>75</v>
@@ -3619,10 +3740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3642,23 +3763,21 @@
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
@@ -3682,13 +3801,13 @@
         <v>75</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -3706,7 +3825,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3724,7 +3843,7 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>75</v>
@@ -3732,10 +3851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3746,7 +3865,7 @@
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -3755,18 +3874,20 @@
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -3815,25 +3936,25 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
@@ -3841,14 +3962,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3864,20 +3985,18 @@
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -3926,7 +4045,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3938,13 +4057,13 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -3952,46 +4071,44 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4039,25 +4156,25 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>75</v>
@@ -4065,10 +4182,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4076,7 +4193,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>86</v>
@@ -4088,19 +4205,21 @@
         <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4148,10 +4267,10 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>86</v>
@@ -4166,7 +4285,7 @@
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
@@ -4185,7 +4304,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>86</v>
@@ -4197,18 +4316,20 @@
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4257,10 +4378,10 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>86</v>
@@ -4275,7 +4396,7 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>75</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>75</v>
@@ -4283,10 +4404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4309,16 +4430,20 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4366,7 +4491,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4384,18 +4509,18 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>75</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4418,19 +4543,17 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4455,13 +4578,13 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>75</v>
+        <v>269</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4479,7 +4602,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4494,10 +4617,10 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -4505,10 +4628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4531,17 +4654,19 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4590,7 +4715,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4608,7 +4733,7 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>75</v>
@@ -4616,10 +4741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4630,7 +4755,7 @@
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4642,17 +4767,15 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -4677,13 +4800,13 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>221</v>
+        <v>75</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4701,25 +4824,25 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>75</v>
@@ -4727,14 +4850,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4753,16 +4876,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>277</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4812,7 +4935,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4824,13 +4947,13 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>281</v>
+        <v>168</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>75</v>
@@ -4838,14 +4961,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4858,24 +4981,26 @@
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -4923,7 +5048,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4935,7 +5060,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4949,10 +5074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4960,10 +5085,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -4975,18 +5100,16 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>291</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -5034,13 +5157,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5052,9 +5175,895 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>75</v>
       </c>
     </row>
